--- a/artfynd/A 50418-2024 artfynd.xlsx
+++ b/artfynd/A 50418-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105343693</v>
+        <v>105343696</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579534.8657771086</v>
+        <v>579606</v>
       </c>
       <c r="R2" t="n">
-        <v>7016061.465893552</v>
+        <v>7016146</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105343701</v>
+        <v>105343697</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579547.9962429059</v>
+        <v>579643</v>
       </c>
       <c r="R3" t="n">
-        <v>7016205.481777385</v>
+        <v>7016147</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,19 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105343695</v>
+        <v>105343694</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579583.9911644014</v>
+        <v>579582</v>
       </c>
       <c r="R4" t="n">
-        <v>7016136.103128409</v>
+        <v>7016116</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105343696</v>
+        <v>105343695</v>
       </c>
       <c r="B5" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579605.8456981489</v>
+        <v>579584</v>
       </c>
       <c r="R5" t="n">
-        <v>7016146.102820856</v>
+        <v>7016136</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105343697</v>
+        <v>105343699</v>
       </c>
       <c r="B6" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579642.8208532357</v>
+        <v>579668</v>
       </c>
       <c r="R6" t="n">
-        <v>7016146.567000921</v>
+        <v>7016159</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,19 +1180,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105343699</v>
+        <v>105343700</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579668.6764506669</v>
+        <v>579686</v>
       </c>
       <c r="R7" t="n">
-        <v>7016158.918302528</v>
+        <v>7016151</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,19 +1248,14 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,12 +1289,7 @@
         <v>105343698</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579638.786101588</v>
+        <v>579639</v>
       </c>
       <c r="R8" t="n">
-        <v>7016145.566291418</v>
+        <v>7016146</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,19 +1354,9 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1485,122 +1385,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>105343694</v>
-      </c>
-      <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Gideåberg värdetrakt, Ång</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>579582.2269492284</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7016116.239945314</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Helgum</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Erland Lindblad, Steve Daurer, Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>

--- a/artfynd/A 50418-2024 artfynd.xlsx
+++ b/artfynd/A 50418-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343696</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343697</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343694</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343695</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343699</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343700</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,8 +1424,22 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105343698</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>